--- a/S15/T174/S15_T174_decision_4.xlsx
+++ b/S15/T174/S15_T174_decision_4.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="71">
   <si>
     <t xml:space="preserve">c1</t>
   </si>
@@ -139,78 +139,81 @@
     <t xml:space="preserve">x 1 batch</t>
   </si>
   <si>
+    <t xml:space="preserve">Rauma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puree Purchasing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">x 1 bin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kemijarvi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concentrate Purchasing for Arnhem</t>
+  </si>
+  <si>
     <t xml:space="preserve">Berlin</t>
   </si>
   <si>
-    <t xml:space="preserve">Puree Purchasing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">x 1 bin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Concentrate Purchasing for Arnhem</t>
+    <t xml:space="preserve">Warsaw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budapest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cordial packaging</t>
+  </si>
+  <si>
+    <t xml:space="preserve">x 20 pallets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cordial production</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bottle Purchasing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sugar Purchasing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">x 1 tonne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concentrate Purchasing for Vesoul</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCFFCC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intercontinental transport</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puree transport to Arnhem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concentrate transport to Arnhem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Milan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concentrate transport to Vesoul</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FFFF99</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production in New-Zeland</t>
   </si>
   <si>
     <t xml:space="preserve">Madrid</t>
   </si>
   <si>
-    <t xml:space="preserve">Cordial packaging</t>
-  </si>
-  <si>
-    <t xml:space="preserve">x 20 pallets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cordial production</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bottle Purchasing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rauma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sugar Purchasing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">x 1 tonne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kemijarvi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Concentrate Purchasing for Vesoul</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCFFCC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Warsaw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intercontinental transport</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bucharest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Budapest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puree transport to Arnhem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Concentrate transport to Arnhem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Concentrate transport to Vesoul</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FFFF99</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production in New-Zeland</t>
-  </si>
-  <si>
     <t xml:space="preserve">Auckland factory</t>
   </si>
   <si>
@@ -223,13 +226,7 @@
     <t xml:space="preserve">Puree sale</t>
   </si>
   <si>
-    <t xml:space="preserve">Milan</t>
-  </si>
-  <si>
     <t xml:space="preserve">Concentrate sale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rome</t>
   </si>
   <si>
     <t xml:space="preserve">FF99CC</t>
@@ -1577,7 +1574,9 @@
       <c r="C11" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="23"/>
+      <c r="D11" s="23" t="n">
+        <v>66</v>
+      </c>
       <c r="E11" s="24"/>
       <c r="F11" s="24"/>
       <c r="G11" s="25"/>
@@ -1592,7 +1591,7 @@
         <v>26</v>
       </c>
       <c r="K11" s="28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L11" s="29" t="s">
         <v>27</v>
@@ -1609,7 +1608,9 @@
         <v>29</v>
       </c>
       <c r="D12" s="30"/>
-      <c r="E12" s="31"/>
+      <c r="E12" s="31" t="n">
+        <v>11</v>
+      </c>
       <c r="F12" s="31"/>
       <c r="G12" s="32"/>
       <c r="H12" s="26" t="str">
@@ -1653,9 +1654,7 @@
       <c r="J13" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="K13" s="34" t="n">
-        <v>0</v>
-      </c>
+      <c r="K13" s="34"/>
       <c r="L13" s="35" t="s">
         <v>35</v>
       </c>
@@ -1680,9 +1679,7 @@
       <c r="J14" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="K14" s="34" t="n">
-        <v>0</v>
-      </c>
+      <c r="K14" s="34"/>
       <c r="L14" s="35" t="s">
         <v>35</v>
       </c>
@@ -1692,13 +1689,13 @@
         <v>5</v>
       </c>
       <c r="B15" s="40" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C15" s="41" t="s">
         <v>22</v>
       </c>
       <c r="D15" s="31" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="E15" s="31"/>
       <c r="F15" s="31"/>
@@ -1714,7 +1711,7 @@
         <v>37</v>
       </c>
       <c r="K15" s="34" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L15" s="35" t="s">
         <v>38</v>
@@ -1725,7 +1722,7 @@
         <v>6</v>
       </c>
       <c r="B16" s="40" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C16" s="41" t="s">
         <v>39</v>
@@ -1733,9 +1730,11 @@
       <c r="D16" s="31"/>
       <c r="E16" s="31"/>
       <c r="F16" s="31" t="n">
-        <v>16</v>
-      </c>
-      <c r="G16" s="32"/>
+        <v>25</v>
+      </c>
+      <c r="G16" s="32" t="n">
+        <v>5</v>
+      </c>
       <c r="H16" s="26" t="str">
         <f aca="false">IF(AND(B16="",OR(C16&lt;&gt;"",D16&lt;&gt;"",E16&lt;&gt;"",F16&lt;&gt;"",G16&lt;&gt;"")),"A lorry must be selected",IF(AND(C16="",OR(D16&lt;&gt;"",E16&lt;&gt;"",F16&lt;&gt;"",G16&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
@@ -1746,9 +1745,7 @@
       <c r="J16" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="K16" s="34" t="n">
-        <v>0</v>
-      </c>
+      <c r="K16" s="34"/>
       <c r="L16" s="35" t="s">
         <v>41</v>
       </c>
@@ -1758,17 +1755,19 @@
         <v>7</v>
       </c>
       <c r="B17" s="40" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C17" s="41" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="D17" s="31"/>
-      <c r="E17" s="31" t="n">
-        <v>15</v>
-      </c>
-      <c r="F17" s="31"/>
-      <c r="G17" s="32"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="31" t="n">
+        <v>30</v>
+      </c>
+      <c r="G17" s="32" t="n">
+        <v>6</v>
+      </c>
       <c r="H17" s="26" t="str">
         <f aca="false">IF(AND(B17="",OR(C17&lt;&gt;"",D17&lt;&gt;"",E17&lt;&gt;"",F17&lt;&gt;"",G17&lt;&gt;"")),"A lorry must be selected",IF(AND(C17="",OR(D17&lt;&gt;"",E17&lt;&gt;"",F17&lt;&gt;"",G17&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
@@ -1777,11 +1776,9 @@
         <v>7</v>
       </c>
       <c r="J17" s="42" t="s">
-        <v>42</v>
-      </c>
-      <c r="K17" s="43" t="n">
-        <v>0</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="K17" s="43"/>
       <c r="L17" s="44" t="s">
         <v>41</v>
       </c>
@@ -1794,16 +1791,14 @@
         <v>25</v>
       </c>
       <c r="C18" s="41" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D18" s="31"/>
       <c r="E18" s="31"/>
       <c r="F18" s="31" t="n">
-        <v>20</v>
-      </c>
-      <c r="G18" s="32" t="n">
-        <v>15</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="G18" s="32"/>
       <c r="H18" s="26" t="str">
         <f aca="false">IF(AND(B18="",OR(C18&lt;&gt;"",D18&lt;&gt;"",E18&lt;&gt;"",F18&lt;&gt;"",G18&lt;&gt;"")),"A lorry must be selected",IF(AND(C18="",OR(D18&lt;&gt;"",E18&lt;&gt;"",F18&lt;&gt;"",G18&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
@@ -1817,12 +1812,12 @@
         <v>25</v>
       </c>
       <c r="C19" s="41" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D19" s="31"/>
       <c r="E19" s="31"/>
       <c r="F19" s="31" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="G19" s="32"/>
       <c r="H19" s="26" t="str">
@@ -1837,11 +1832,17 @@
       <c r="A20" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B20" s="40"/>
-      <c r="C20" s="41"/>
+      <c r="B20" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="41" t="s">
+        <v>46</v>
+      </c>
       <c r="D20" s="31"/>
       <c r="E20" s="31"/>
-      <c r="F20" s="31"/>
+      <c r="F20" s="31" t="n">
+        <v>29</v>
+      </c>
       <c r="G20" s="32"/>
       <c r="H20" s="26" t="str">
         <f aca="false">IF(AND(B20="",OR(C20&lt;&gt;"",D20&lt;&gt;"",E20&lt;&gt;"",F20&lt;&gt;"",G20&lt;&gt;"")),"A lorry must be selected",IF(AND(C20="",OR(D20&lt;&gt;"",E20&lt;&gt;"",F20&lt;&gt;"",G20&lt;&gt;"")),"A town must be selected",""))</f>
@@ -1852,16 +1853,10 @@
       <c r="A21" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B21" s="40" t="s">
-        <v>32</v>
-      </c>
-      <c r="C21" s="41" t="s">
-        <v>29</v>
-      </c>
+      <c r="B21" s="40"/>
+      <c r="C21" s="41"/>
       <c r="D21" s="31"/>
-      <c r="E21" s="31" t="n">
-        <v>24</v>
-      </c>
+      <c r="E21" s="31"/>
       <c r="F21" s="31"/>
       <c r="G21" s="32"/>
       <c r="H21" s="26" t="str">
@@ -1872,13 +1867,13 @@
         <v>1</v>
       </c>
       <c r="J21" s="45" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K21" s="28" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L21" s="45" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1886,17 +1881,17 @@
         <v>12</v>
       </c>
       <c r="B22" s="40" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C22" s="41" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D22" s="31"/>
-      <c r="E22" s="31"/>
+      <c r="E22" s="31" t="n">
+        <v>25</v>
+      </c>
       <c r="F22" s="31"/>
-      <c r="G22" s="32" t="n">
-        <v>24</v>
-      </c>
+      <c r="G22" s="32"/>
       <c r="H22" s="26" t="str">
         <f aca="false">IF(AND(B22="",OR(C22&lt;&gt;"",D22&lt;&gt;"",E22&lt;&gt;"",F22&lt;&gt;"",G22&lt;&gt;"")),"A lorry must be selected",IF(AND(C22="",OR(D22&lt;&gt;"",E22&lt;&gt;"",F22&lt;&gt;"",G22&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
@@ -1905,10 +1900,10 @@
         <v>2</v>
       </c>
       <c r="J22" s="46" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K22" s="34" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L22" s="46" t="s">
         <v>31</v>
@@ -1918,12 +1913,18 @@
       <c r="A23" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B23" s="40"/>
-      <c r="C23" s="41"/>
+      <c r="B23" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23" s="41" t="s">
+        <v>44</v>
+      </c>
       <c r="D23" s="31"/>
       <c r="E23" s="31"/>
       <c r="F23" s="31"/>
-      <c r="G23" s="32"/>
+      <c r="G23" s="32" t="n">
+        <v>5</v>
+      </c>
       <c r="H23" s="26" t="str">
         <f aca="false">IF(AND(B23="",OR(C23&lt;&gt;"",D23&lt;&gt;"",E23&lt;&gt;"",F23&lt;&gt;"",G23&lt;&gt;"")),"A lorry must be selected",IF(AND(C23="",OR(D23&lt;&gt;"",E23&lt;&gt;"",F23&lt;&gt;"",G23&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
@@ -1948,7 +1949,7 @@
       </c>
       <c r="P23" s="2" t="str">
         <f aca="false">IF(AND(C23&lt;&gt;"",OR(D23&lt;&gt;"",E23&lt;&gt;"",F23&lt;&gt;"",G23&lt;&gt;"")),"A town must be selected","")</f>
-        <v/>
+        <v>A town must be selected</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1956,17 +1957,17 @@
         <v>14</v>
       </c>
       <c r="B24" s="40" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C24" s="41" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="D24" s="31"/>
-      <c r="E24" s="31" t="n">
-        <v>50</v>
-      </c>
+      <c r="E24" s="31"/>
       <c r="F24" s="31"/>
-      <c r="G24" s="32"/>
+      <c r="G24" s="32" t="n">
+        <v>6</v>
+      </c>
       <c r="H24" s="26" t="str">
         <f aca="false">IF(AND(B24="",OR(C24&lt;&gt;"",D24&lt;&gt;"",E24&lt;&gt;"",F24&lt;&gt;"",G24&lt;&gt;"")),"A lorry must be selected",IF(AND(C24="",OR(D24&lt;&gt;"",E24&lt;&gt;"",F24&lt;&gt;"",G24&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
@@ -1977,9 +1978,7 @@
       <c r="J24" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="K24" s="34" t="n">
-        <v>1</v>
-      </c>
+      <c r="K24" s="34"/>
       <c r="L24" s="46" t="s">
         <v>35</v>
       </c>
@@ -1989,16 +1988,16 @@
         <v>15</v>
       </c>
       <c r="B25" s="40" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C25" s="41" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="D25" s="31"/>
       <c r="E25" s="31"/>
       <c r="F25" s="31"/>
       <c r="G25" s="32" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H25" s="26" t="str">
         <f aca="false">IF(AND(B25="",OR(C25&lt;&gt;"",D25&lt;&gt;"",E25&lt;&gt;"",F25&lt;&gt;"",G25&lt;&gt;"")),"A lorry must be selected",IF(AND(C25="",OR(D25&lt;&gt;"",E25&lt;&gt;"",F25&lt;&gt;"",G25&lt;&gt;"")),"A town must be selected",""))</f>
@@ -2008,10 +2007,10 @@
         <v>5</v>
       </c>
       <c r="J25" s="46" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K25" s="34" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L25" s="46" t="s">
         <v>38</v>
@@ -2021,18 +2020,12 @@
       <c r="A26" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B26" s="40" t="s">
-        <v>28</v>
-      </c>
-      <c r="C26" s="41" t="s">
-        <v>48</v>
-      </c>
+      <c r="B26" s="40"/>
+      <c r="C26" s="41"/>
       <c r="D26" s="31"/>
       <c r="E26" s="31"/>
       <c r="F26" s="31"/>
-      <c r="G26" s="32" t="n">
-        <v>17</v>
-      </c>
+      <c r="G26" s="32"/>
       <c r="H26" s="26" t="str">
         <f aca="false">IF(AND(B26="",OR(C26&lt;&gt;"",D26&lt;&gt;"",E26&lt;&gt;"",F26&lt;&gt;"",G26&lt;&gt;"")),"A lorry must be selected",IF(AND(C26="",OR(D26&lt;&gt;"",E26&lt;&gt;"",F26&lt;&gt;"",G26&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
@@ -2041,13 +2034,13 @@
         <v>6</v>
       </c>
       <c r="J26" s="46" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K26" s="34" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="L26" s="46" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2055,17 +2048,17 @@
         <v>17</v>
       </c>
       <c r="B27" s="40" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C27" s="41" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="D27" s="31"/>
-      <c r="E27" s="31"/>
+      <c r="E27" s="31" t="n">
+        <v>11</v>
+      </c>
       <c r="F27" s="31"/>
-      <c r="G27" s="32" t="n">
-        <v>17</v>
-      </c>
+      <c r="G27" s="32"/>
       <c r="H27" s="26" t="str">
         <f aca="false">IF(AND(B27="",OR(C27&lt;&gt;"",D27&lt;&gt;"",E27&lt;&gt;"",F27&lt;&gt;"",G27&lt;&gt;"")),"A lorry must be selected",IF(AND(C27="",OR(D27&lt;&gt;"",E27&lt;&gt;"",F27&lt;&gt;"",G27&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
@@ -2074,11 +2067,9 @@
         <v>7</v>
       </c>
       <c r="J27" s="47" t="s">
-        <v>52</v>
-      </c>
-      <c r="K27" s="43" t="n">
-        <v>0</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="K27" s="43"/>
       <c r="L27" s="47" t="s">
         <v>41</v>
       </c>
@@ -2098,23 +2089,17 @@
         <v/>
       </c>
       <c r="J28" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="B29" s="40" t="s">
-        <v>28</v>
-      </c>
-      <c r="C29" s="41" t="s">
-        <v>29</v>
-      </c>
+      <c r="B29" s="40"/>
+      <c r="C29" s="41"/>
       <c r="D29" s="31"/>
-      <c r="E29" s="31" t="n">
-        <v>50</v>
-      </c>
+      <c r="E29" s="31"/>
       <c r="F29" s="31"/>
       <c r="G29" s="32"/>
       <c r="H29" s="26" t="str">
@@ -2126,18 +2111,12 @@
       <c r="A30" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="B30" s="40" t="s">
-        <v>28</v>
-      </c>
-      <c r="C30" s="41" t="s">
-        <v>54</v>
-      </c>
+      <c r="B30" s="40"/>
+      <c r="C30" s="41"/>
       <c r="D30" s="31"/>
       <c r="E30" s="31"/>
       <c r="F30" s="31"/>
-      <c r="G30" s="32" t="n">
-        <v>8</v>
-      </c>
+      <c r="G30" s="32"/>
       <c r="H30" s="26" t="str">
         <f aca="false">IF(AND(B30="",OR(C30&lt;&gt;"",D30&lt;&gt;"",E30&lt;&gt;"",F30&lt;&gt;"",G30&lt;&gt;"")),"A lorry must be selected",IF(AND(C30="",OR(D30&lt;&gt;"",E30&lt;&gt;"",F30&lt;&gt;"",G30&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
@@ -2153,16 +2132,16 @@
         <v>21</v>
       </c>
       <c r="B31" s="40" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C31" s="41" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="D31" s="31"/>
       <c r="E31" s="31"/>
       <c r="F31" s="31"/>
       <c r="G31" s="32" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="H31" s="26" t="str">
         <f aca="false">IF(AND(B31="",OR(C31&lt;&gt;"",D31&lt;&gt;"",E31&lt;&gt;"",F31&lt;&gt;"",G31&lt;&gt;"")),"A lorry must be selected",IF(AND(C31="",OR(D31&lt;&gt;"",E31&lt;&gt;"",F31&lt;&gt;"",G31&lt;&gt;"")),"A town must be selected",""))</f>
@@ -2173,18 +2152,12 @@
       <c r="A32" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="B32" s="40" t="s">
-        <v>28</v>
-      </c>
-      <c r="C32" s="41" t="s">
-        <v>57</v>
-      </c>
+      <c r="B32" s="40"/>
+      <c r="C32" s="41"/>
       <c r="D32" s="31"/>
       <c r="E32" s="31"/>
       <c r="F32" s="31"/>
-      <c r="G32" s="32" t="n">
-        <v>23</v>
-      </c>
+      <c r="G32" s="32"/>
       <c r="H32" s="26" t="str">
         <f aca="false">IF(AND(B32="",OR(C32&lt;&gt;"",D32&lt;&gt;"",E32&lt;&gt;"",F32&lt;&gt;"",G32&lt;&gt;"")),"A lorry must be selected",IF(AND(C32="",OR(D32&lt;&gt;"",E32&lt;&gt;"",F32&lt;&gt;"",G32&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
@@ -2193,7 +2166,7 @@
         <v>1</v>
       </c>
       <c r="J32" s="49" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="K32" s="28"/>
       <c r="L32" s="49" t="s">
@@ -2204,9 +2177,15 @@
       <c r="A33" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="B33" s="40"/>
-      <c r="C33" s="41"/>
-      <c r="D33" s="31"/>
+      <c r="B33" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="C33" s="41" t="s">
+        <v>22</v>
+      </c>
+      <c r="D33" s="31" t="n">
+        <v>24</v>
+      </c>
       <c r="E33" s="31"/>
       <c r="F33" s="31"/>
       <c r="G33" s="32"/>
@@ -2218,7 +2197,7 @@
         <v>2</v>
       </c>
       <c r="J33" s="50" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="K33" s="34"/>
       <c r="L33" s="50" t="s">
@@ -2230,16 +2209,16 @@
         <v>24</v>
       </c>
       <c r="B34" s="40" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C34" s="41" t="s">
-        <v>22</v>
-      </c>
-      <c r="D34" s="31" t="n">
-        <v>66</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D34" s="31"/>
       <c r="E34" s="31"/>
-      <c r="F34" s="31"/>
+      <c r="F34" s="31" t="n">
+        <v>12</v>
+      </c>
       <c r="G34" s="32"/>
       <c r="H34" s="26" t="str">
         <f aca="false">IF(AND(B34="",OR(C34&lt;&gt;"",D34&lt;&gt;"",E34&lt;&gt;"",F34&lt;&gt;"",G34&lt;&gt;"")),"A lorry must be selected",IF(AND(C34="",OR(D34&lt;&gt;"",E34&lt;&gt;"",F34&lt;&gt;"",G34&lt;&gt;"")),"A town must be selected",""))</f>
@@ -2249,7 +2228,7 @@
         <v>3</v>
       </c>
       <c r="J34" s="51" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K34" s="43"/>
       <c r="L34" s="51" t="s">
@@ -2261,15 +2240,15 @@
         <v>25</v>
       </c>
       <c r="B35" s="40" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C35" s="41" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="D35" s="31"/>
       <c r="E35" s="31"/>
       <c r="F35" s="31" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="G35" s="32"/>
       <c r="H35" s="26" t="str">
@@ -2285,16 +2264,16 @@
         <v>26</v>
       </c>
       <c r="B36" s="40" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C36" s="41" t="s">
-        <v>51</v>
-      </c>
-      <c r="D36" s="31"/>
+        <v>22</v>
+      </c>
+      <c r="D36" s="31" t="n">
+        <v>24</v>
+      </c>
       <c r="E36" s="31"/>
-      <c r="F36" s="31" t="n">
-        <v>33</v>
-      </c>
+      <c r="F36" s="31"/>
       <c r="G36" s="32"/>
       <c r="H36" s="26" t="str">
         <f aca="false">IF(AND(B36="",OR(C36&lt;&gt;"",D36&lt;&gt;"",E36&lt;&gt;"",F36&lt;&gt;"",G36&lt;&gt;"")),"A lorry must be selected",IF(AND(C36="",OR(D36&lt;&gt;"",E36&lt;&gt;"",F36&lt;&gt;"",G36&lt;&gt;"")),"A town must be selected",""))</f>
@@ -2325,15 +2304,9 @@
       <c r="A38" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="B38" s="40" t="s">
-        <v>25</v>
-      </c>
-      <c r="C38" s="41" t="s">
-        <v>22</v>
-      </c>
-      <c r="D38" s="31" t="n">
-        <v>66</v>
-      </c>
+      <c r="B38" s="40"/>
+      <c r="C38" s="41"/>
+      <c r="D38" s="31"/>
       <c r="E38" s="31"/>
       <c r="F38" s="31"/>
       <c r="G38" s="32"/>
@@ -2347,15 +2320,15 @@
         <v>29</v>
       </c>
       <c r="B39" s="40" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C39" s="41" t="s">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="D39" s="31"/>
       <c r="E39" s="31"/>
       <c r="F39" s="31" t="n">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="G39" s="32"/>
       <c r="H39" s="26" t="str">
@@ -2363,7 +2336,7 @@
         <v/>
       </c>
       <c r="J39" s="53" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2399,11 +2372,13 @@
         <v>1</v>
       </c>
       <c r="J41" s="55" t="s">
-        <v>64</v>
-      </c>
-      <c r="K41" s="28"/>
+        <v>65</v>
+      </c>
+      <c r="K41" s="28" t="n">
+        <v>15</v>
+      </c>
       <c r="L41" s="55" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M41" s="56"/>
     </row>
@@ -2461,15 +2436,9 @@
       <c r="A44" s="1" t="n">
         <v>34</v>
       </c>
-      <c r="B44" s="40" t="s">
-        <v>28</v>
-      </c>
-      <c r="C44" s="41" t="s">
-        <v>29</v>
-      </c>
-      <c r="D44" s="31" t="n">
-        <v>66</v>
-      </c>
+      <c r="B44" s="40"/>
+      <c r="C44" s="41"/>
+      <c r="D44" s="31"/>
       <c r="E44" s="31"/>
       <c r="F44" s="31"/>
       <c r="G44" s="32"/>
@@ -2481,10 +2450,10 @@
         <v>4</v>
       </c>
       <c r="J44" s="57" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K44" s="34" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="L44" s="57" t="s">
         <v>41</v>
@@ -2494,17 +2463,11 @@
       <c r="A45" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="B45" s="40" t="s">
-        <v>28</v>
-      </c>
-      <c r="C45" s="41" t="s">
-        <v>67</v>
-      </c>
+      <c r="B45" s="40"/>
+      <c r="C45" s="41"/>
       <c r="D45" s="31"/>
       <c r="E45" s="31"/>
-      <c r="F45" s="31" t="n">
-        <v>33</v>
-      </c>
+      <c r="F45" s="31"/>
       <c r="G45" s="32"/>
       <c r="H45" s="26" t="str">
         <f aca="false">IF(AND(B45="",OR(C45&lt;&gt;"",D45&lt;&gt;"",E45&lt;&gt;"",F45&lt;&gt;"",G45&lt;&gt;"")),"A lorry must be selected",IF(AND(C45="",OR(D45&lt;&gt;"",E45&lt;&gt;"",F45&lt;&gt;"",G45&lt;&gt;"")),"A town must be selected",""))</f>
@@ -2525,39 +2488,27 @@
       <c r="A46" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="B46" s="40" t="s">
-        <v>28</v>
-      </c>
-      <c r="C46" s="41" t="s">
-        <v>69</v>
-      </c>
+      <c r="B46" s="40"/>
+      <c r="C46" s="41"/>
       <c r="D46" s="31"/>
       <c r="E46" s="31"/>
-      <c r="F46" s="31" t="n">
-        <v>33</v>
-      </c>
+      <c r="F46" s="31"/>
       <c r="G46" s="32"/>
       <c r="H46" s="26" t="str">
         <f aca="false">IF(AND(B46="",OR(C46&lt;&gt;"",D46&lt;&gt;"",E46&lt;&gt;"",F46&lt;&gt;"",G46&lt;&gt;"")),"A lorry must be selected",IF(AND(C46="",OR(D46&lt;&gt;"",E46&lt;&gt;"",F46&lt;&gt;"",G46&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
       </c>
       <c r="J46" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="n">
         <v>37</v>
       </c>
-      <c r="B47" s="40" t="s">
-        <v>25</v>
-      </c>
-      <c r="C47" s="41" t="s">
-        <v>22</v>
-      </c>
-      <c r="D47" s="31" t="n">
-        <v>66</v>
-      </c>
+      <c r="B47" s="40"/>
+      <c r="C47" s="41"/>
+      <c r="D47" s="31"/>
       <c r="E47" s="31"/>
       <c r="F47" s="31"/>
       <c r="G47" s="32"/>
@@ -2570,17 +2521,11 @@
       <c r="A48" s="1" t="n">
         <v>38</v>
       </c>
-      <c r="B48" s="40" t="s">
-        <v>25</v>
-      </c>
-      <c r="C48" s="41" t="s">
-        <v>54</v>
-      </c>
+      <c r="B48" s="40"/>
+      <c r="C48" s="41"/>
       <c r="D48" s="31"/>
       <c r="E48" s="31"/>
-      <c r="F48" s="31" t="n">
-        <v>24</v>
-      </c>
+      <c r="F48" s="31"/>
       <c r="G48" s="32"/>
       <c r="H48" s="26" t="str">
         <f aca="false">IF(AND(B48="",OR(C48&lt;&gt;"",D48&lt;&gt;"",E48&lt;&gt;"",F48&lt;&gt;"",G48&lt;&gt;"")),"A lorry must be selected",IF(AND(C48="",OR(D48&lt;&gt;"",E48&lt;&gt;"",F48&lt;&gt;"",G48&lt;&gt;"")),"A town must be selected",""))</f>
@@ -2591,17 +2536,11 @@
       <c r="A49" s="1" t="n">
         <v>39</v>
       </c>
-      <c r="B49" s="40" t="s">
-        <v>25</v>
-      </c>
-      <c r="C49" s="41" t="s">
-        <v>56</v>
-      </c>
+      <c r="B49" s="40"/>
+      <c r="C49" s="41"/>
       <c r="D49" s="31"/>
       <c r="E49" s="31"/>
-      <c r="F49" s="31" t="n">
-        <v>14</v>
-      </c>
+      <c r="F49" s="31"/>
       <c r="G49" s="32"/>
       <c r="H49" s="26" t="str">
         <f aca="false">IF(AND(B49="",OR(C49&lt;&gt;"",D49&lt;&gt;"",E49&lt;&gt;"",F49&lt;&gt;"",G49&lt;&gt;"")),"A lorry must be selected",IF(AND(C49="",OR(D49&lt;&gt;"",E49&lt;&gt;"",F49&lt;&gt;"",G49&lt;&gt;"")),"A town must be selected",""))</f>
@@ -2612,17 +2551,11 @@
       <c r="A50" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="B50" s="40" t="s">
-        <v>25</v>
-      </c>
-      <c r="C50" s="41" t="s">
-        <v>57</v>
-      </c>
+      <c r="B50" s="40"/>
+      <c r="C50" s="41"/>
       <c r="D50" s="31"/>
       <c r="E50" s="31"/>
-      <c r="F50" s="31" t="n">
-        <v>28</v>
-      </c>
+      <c r="F50" s="31"/>
       <c r="G50" s="32"/>
       <c r="H50" s="26" t="str">
         <f aca="false">IF(AND(B50="",OR(C50&lt;&gt;"",D50&lt;&gt;"",E50&lt;&gt;"",F50&lt;&gt;"",G50&lt;&gt;"")),"A lorry must be selected",IF(AND(C50="",OR(D50&lt;&gt;"",E50&lt;&gt;"",F50&lt;&gt;"",G50&lt;&gt;"")),"A town must be selected",""))</f>
@@ -2648,16 +2581,10 @@
       <c r="A52" s="1" t="n">
         <v>42</v>
       </c>
-      <c r="B52" s="40" t="s">
-        <v>32</v>
-      </c>
-      <c r="C52" s="41" t="s">
-        <v>29</v>
-      </c>
+      <c r="B52" s="40"/>
+      <c r="C52" s="41"/>
       <c r="D52" s="31"/>
-      <c r="E52" s="31" t="n">
-        <v>24</v>
-      </c>
+      <c r="E52" s="31"/>
       <c r="F52" s="31"/>
       <c r="G52" s="32"/>
       <c r="H52" s="26" t="str">
@@ -2669,18 +2596,12 @@
       <c r="A53" s="1" t="n">
         <v>43</v>
       </c>
-      <c r="B53" s="40" t="s">
-        <v>32</v>
-      </c>
-      <c r="C53" s="41" t="s">
-        <v>33</v>
-      </c>
+      <c r="B53" s="40"/>
+      <c r="C53" s="41"/>
       <c r="D53" s="31"/>
       <c r="E53" s="31"/>
       <c r="F53" s="31"/>
-      <c r="G53" s="32" t="n">
-        <v>24</v>
-      </c>
+      <c r="G53" s="32"/>
       <c r="H53" s="26" t="str">
         <f aca="false">IF(AND(B53="",OR(C53&lt;&gt;"",D53&lt;&gt;"",E53&lt;&gt;"",F53&lt;&gt;"",G53&lt;&gt;"")),"A lorry must be selected",IF(AND(C53="",OR(D53&lt;&gt;"",E53&lt;&gt;"",F53&lt;&gt;"",G53&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
@@ -2705,16 +2626,10 @@
       <c r="A55" s="1" t="n">
         <v>45</v>
       </c>
-      <c r="B55" s="40" t="s">
-        <v>32</v>
-      </c>
-      <c r="C55" s="41" t="s">
-        <v>29</v>
-      </c>
+      <c r="B55" s="40"/>
+      <c r="C55" s="41"/>
       <c r="D55" s="31"/>
-      <c r="E55" s="31" t="n">
-        <v>24</v>
-      </c>
+      <c r="E55" s="31"/>
       <c r="F55" s="31"/>
       <c r="G55" s="32"/>
       <c r="H55" s="26" t="str">
@@ -2726,18 +2641,12 @@
       <c r="A56" s="1" t="n">
         <v>46</v>
       </c>
-      <c r="B56" s="40" t="s">
-        <v>32</v>
-      </c>
-      <c r="C56" s="41" t="s">
-        <v>33</v>
-      </c>
+      <c r="B56" s="40"/>
+      <c r="C56" s="41"/>
       <c r="D56" s="31"/>
       <c r="E56" s="31"/>
       <c r="F56" s="31"/>
-      <c r="G56" s="32" t="n">
-        <v>24</v>
-      </c>
+      <c r="G56" s="32"/>
       <c r="H56" s="26" t="str">
         <f aca="false">IF(AND(B56="",OR(C56&lt;&gt;"",D56&lt;&gt;"",E56&lt;&gt;"",F56&lt;&gt;"",G56&lt;&gt;"")),"A lorry must be selected",IF(AND(C56="",OR(D56&lt;&gt;"",E56&lt;&gt;"",F56&lt;&gt;"",G56&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
@@ -2762,16 +2671,10 @@
       <c r="A58" s="1" t="n">
         <v>48</v>
       </c>
-      <c r="B58" s="40" t="s">
-        <v>32</v>
-      </c>
-      <c r="C58" s="41" t="s">
-        <v>29</v>
-      </c>
+      <c r="B58" s="40"/>
+      <c r="C58" s="41"/>
       <c r="D58" s="31"/>
-      <c r="E58" s="31" t="n">
-        <v>17</v>
-      </c>
+      <c r="E58" s="31"/>
       <c r="F58" s="31"/>
       <c r="G58" s="32"/>
       <c r="H58" s="26" t="str">
@@ -2783,18 +2686,12 @@
       <c r="A59" s="1" t="n">
         <v>49</v>
       </c>
-      <c r="B59" s="40" t="s">
-        <v>32</v>
-      </c>
-      <c r="C59" s="41" t="s">
-        <v>39</v>
-      </c>
+      <c r="B59" s="40"/>
+      <c r="C59" s="41"/>
       <c r="D59" s="31"/>
       <c r="E59" s="31"/>
       <c r="F59" s="31"/>
-      <c r="G59" s="32" t="n">
-        <v>17</v>
-      </c>
+      <c r="G59" s="32"/>
       <c r="H59" s="26" t="str">
         <f aca="false">IF(AND(B59="",OR(C59&lt;&gt;"",D59&lt;&gt;"",E59&lt;&gt;"",F59&lt;&gt;"",G59&lt;&gt;"")),"A lorry must be selected",IF(AND(C59="",OR(D59&lt;&gt;"",E59&lt;&gt;"",F59&lt;&gt;"",G59&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
@@ -2958,7 +2855,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="n">
         <v>60</v>
       </c>
@@ -2970,7 +2867,9 @@
       </c>
       <c r="D70" s="67"/>
       <c r="E70" s="68"/>
-      <c r="F70" s="68"/>
+      <c r="F70" s="68" t="n">
+        <v>12</v>
+      </c>
       <c r="G70" s="69"/>
       <c r="H70" s="26" t="str">
         <f aca="false">IF(AND(B70="",OR(C70&lt;&gt;"",D70&lt;&gt;"",E70&lt;&gt;"",F70&lt;&gt;"",G70&lt;&gt;"")),"A lorry must be selected",IF(AND(C70="",OR(D70&lt;&gt;"",E70&lt;&gt;"",F70&lt;&gt;"",G70&lt;&gt;"")),"A town must be selected",""))</f>
@@ -2979,7 +2878,7 @@
     </row>
     <row r="71" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B71" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
